--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28-FEB-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6842</v>
+        <v>17024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8349</v>
+        <v>20650</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1507</v>
+        <v>-3626</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,27 +577,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>04-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-443</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6656</v>
+        <v>8036</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6804</v>
+        <v>8091</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-148</v>
+        <v>-55</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,7 +608,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-MAR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6842</v>
+        <v>8036</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7513</v>
+        <v>8091</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-671</v>
+        <v>-55</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,7 +653,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-243</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6715</v>
+        <v>7568</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6804</v>
+        <v>8091</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-89</v>
+        <v>-523</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,327 +698,12 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>11-MAR-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-965</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>6656</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>7158</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-502</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>14-MAR-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-243</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>6056</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6081</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19-MAR-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>6056</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>6081</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21-MAR-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-243</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>8413</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>8831</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-418</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>12956</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>14545</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-1589</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26-MAR-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>13658</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>17358</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-3700</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28-MAR-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-243</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>21413</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>24175</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-2762</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-243</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17024</v>
+        <v>9694</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20650</v>
+        <v>10998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3626</v>
+        <v>-1304</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8036</v>
+        <v>9694</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8091</v>
+        <v>10998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-55</v>
+        <v>-1304</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,7 +608,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8036</v>
+        <v>10291</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8091</v>
+        <v>10998</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-55</v>
+        <v>-707</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,7 +653,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,33 +677,843 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>10291</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10998</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-707</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>09-APR-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>8122</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-271</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>09-APR-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>8122</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-271</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7930</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>8894</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-964</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>7930</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8894</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-964</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8122</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-271</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>8122</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-271</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>18-APR-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-295</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>18-APR-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-295</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13-MAY-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-143</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>7568</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8091</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-523</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n">
+        <v>7337</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>9315</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-1978</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>13-MAY-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7337</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>9315</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-1978</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-636</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-636</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>7930</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-557</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>7930</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-557</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>25-MAY-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-636</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>25-MAY-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-636</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10998</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-3147</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>10998</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-3147</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -532,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-443</t>
+          <t>SM-967</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9694</v>
+        <v>7326</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10998</v>
+        <v>7961</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1304</v>
+        <v>-635</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9694</v>
+        <v>7693</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10998</v>
+        <v>8313</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1304</v>
+        <v>-620</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10291</v>
+        <v>7693</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10998</v>
+        <v>7961</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-707</v>
+        <v>-268</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10291</v>
+        <v>12244</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10998</v>
+        <v>17232</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-707</v>
+        <v>-4988</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7851</v>
+        <v>12244</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8122</v>
+        <v>12864</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-271</v>
+        <v>-620</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7851</v>
+        <v>12371</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8122</v>
+        <v>14780</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-271</v>
+        <v>-2409</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,22 +825,22 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7930</v>
+        <v>12606</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8894</v>
+        <v>14780</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-964</v>
+        <v>-2174</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7930</v>
+        <v>8905</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8894</v>
+        <v>14780</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-964</v>
+        <v>-5875</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -906,26 +915,26 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7851</v>
+        <v>9334</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8122</v>
+        <v>14780</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-271</v>
+        <v>-5446</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7851</v>
+        <v>12371</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8122</v>
+        <v>14780</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-271</v>
+        <v>-2409</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8192</v>
+        <v>12371</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-295</v>
+        <v>-2409</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,26 +1050,26 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8192</v>
+        <v>9148</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-295</v>
+        <v>-5632</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13-MAY-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7337</v>
+        <v>12371</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9315</v>
+        <v>14780</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1978</v>
+        <v>-2409</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13-MAY-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7337</v>
+        <v>12371</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9315</v>
+        <v>14780</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1978</v>
+        <v>-2409</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7851</v>
+        <v>9722</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-636</v>
+        <v>-5058</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1193,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7851</v>
+        <v>12371</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-636</v>
+        <v>-2409</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7930</v>
+        <v>12371</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-557</v>
+        <v>-2409</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7930</v>
+        <v>11462</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-557</v>
+        <v>-3318</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7851</v>
+        <v>12371</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-636</v>
+        <v>-2409</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7851</v>
+        <v>14513</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8487</v>
+        <v>14780</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-636</v>
+        <v>-267</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1432,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7851</v>
+        <v>14513</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10998</v>
+        <v>14780</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3147</v>
+        <v>-267</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1463,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1477,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,33 +1496,888 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11525</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-3255</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-3114</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-3114</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-3114</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-3114</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>7851</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>10998</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-3147</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
+      <c r="D35" s="2" t="n">
+        <v>9068</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-5712</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-3114</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>9148</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-5632</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-3677</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>14780</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-3114</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>7214</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>9454</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-2240</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>7214</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>9031</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-1817</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +532,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-967</t>
+          <t>SM-443</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -555,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7326</v>
+        <v>14513</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7961</v>
+        <v>16429</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-635</v>
+        <v>-1916</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7693</v>
+        <v>14122</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8313</v>
+        <v>16429</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-620</v>
+        <v>-2307</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7693</v>
+        <v>8905</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7961</v>
+        <v>13428</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-268</v>
+        <v>-4523</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12244</v>
+        <v>9334</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17232</v>
+        <v>13428</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4988</v>
+        <v>-4094</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12244</v>
+        <v>9148</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12864</v>
+        <v>13428</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-620</v>
+        <v>-4280</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12371</v>
+        <v>9334</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-2409</v>
+        <v>-4094</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12606</v>
+        <v>12244</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2174</v>
+        <v>-1184</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8905</v>
+        <v>11462</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5875</v>
+        <v>-1966</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9334</v>
+        <v>11103</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5446</v>
+        <v>-2325</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12371</v>
+        <v>11103</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2409</v>
+        <v>-2325</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>15</v>
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12371</v>
+        <v>11103</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2409</v>
+        <v>-2325</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>15</v>
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9148</v>
+        <v>11103</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5632</v>
+        <v>-2325</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12371</v>
+        <v>11103</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2409</v>
+        <v>-2325</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>15</v>
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12371</v>
+        <v>11103</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2409</v>
+        <v>-2325</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>15</v>
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1172,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9722</v>
+        <v>9068</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-5058</v>
+        <v>-4360</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1217,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>12371</v>
+        <v>11103</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2409</v>
+        <v>-2325</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>15</v>
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1262,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12371</v>
+        <v>9148</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2409</v>
+        <v>-4280</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1307,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11462</v>
+        <v>11103</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14780</v>
+        <v>13428</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3318</v>
+        <v>-2325</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1352,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>12371</v>
+        <v>7214</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14780</v>
+        <v>7341</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2409</v>
+        <v>-127</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1388,996 +1379,6 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>19-AUG-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>14513</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-267</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26-AUG-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>14513</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-267</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>11525</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-3255</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>11666</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-3114</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>11666</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-3114</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>12-SEP-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12-SEP-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>11666</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-3114</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>11666</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-3114</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>9068</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-5712</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>11666</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>-3114</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>9148</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>-5632</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>11103</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>-3677</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-764</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>11666</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>-3114</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>7214</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>9454</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>-2240</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>7214</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>9031</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>-1817</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14513</v>
+        <v>12924</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16429</v>
+        <v>16260</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1916</v>
+        <v>-3336</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14122</v>
+        <v>10989</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16429</v>
+        <v>13290</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2307</v>
+        <v>-2301</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -636,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8905</v>
+        <v>12118</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4523</v>
+        <v>-1172</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9334</v>
+        <v>11423</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4094</v>
+        <v>-1867</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>20</v>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9148</v>
+        <v>7140</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13428</v>
+        <v>8255</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4280</v>
+        <v>-1115</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9334</v>
+        <v>7140</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13428</v>
+        <v>8255</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4094</v>
+        <v>-1115</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12244</v>
+        <v>7140</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13428</v>
+        <v>8743</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1184</v>
+        <v>-1603</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11462</v>
+        <v>8813</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1966</v>
+        <v>-4477</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11103</v>
+        <v>9238</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2325</v>
+        <v>-4052</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11103</v>
+        <v>9054</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2325</v>
+        <v>-4236</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11103</v>
+        <v>9238</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2325</v>
+        <v>-4052</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11103</v>
+        <v>7140</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2325</v>
+        <v>-6150</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11103</v>
+        <v>11344</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2325</v>
+        <v>-1946</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11103</v>
+        <v>14363</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13428</v>
+        <v>16260</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2325</v>
+        <v>-1897</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9068</v>
+        <v>10989</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4360</v>
+        <v>-2301</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1221,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11103</v>
+        <v>10989</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2325</v>
+        <v>-2301</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>15</v>
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9148</v>
+        <v>10989</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4280</v>
+        <v>-2301</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11103</v>
+        <v>10989</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13428</v>
+        <v>13290</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2325</v>
+        <v>-2301</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>15</v>
@@ -1342,43 +1351,268 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>10989</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-2301</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>8975</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-4315</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>10989</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-2301</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9054</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-4236</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>10989</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-2301</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>23-SEP-26</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-143</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>7214</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>7341</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-127</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
+      <c r="D25" s="2" t="n">
+        <v>7140</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>7265</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12924</v>
+        <v>4853</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16260</v>
+        <v>4908</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3336</v>
+        <v>-55</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,40 +586,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-443</t>
+          <t>SM-967</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10989</v>
+        <v>4853</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13290</v>
+        <v>4908</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2301</v>
+        <v>-55</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12118</v>
+        <v>4853</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13290</v>
+        <v>4908</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1172</v>
+        <v>-55</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11423</v>
+        <v>4853</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13290</v>
+        <v>4908</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1867</v>
+        <v>-55</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7140</v>
+        <v>8813</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8255</v>
+        <v>11295</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1115</v>
+        <v>-2482</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7140</v>
+        <v>13841</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8255</v>
+        <v>16218</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1115</v>
+        <v>-2377</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7140</v>
+        <v>12090</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8743</v>
+        <v>13262</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1603</v>
+        <v>-1172</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8813</v>
+        <v>11312</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4477</v>
+        <v>-1950</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9238</v>
+        <v>7140</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13290</v>
+        <v>8241</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4052</v>
+        <v>-1101</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9054</v>
+        <v>7140</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13290</v>
+        <v>8227</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4236</v>
+        <v>-1087</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9238</v>
+        <v>7140</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13290</v>
+        <v>8241</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4052</v>
+        <v>-1101</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7140</v>
+        <v>7251</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13290</v>
+        <v>8729</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6150</v>
+        <v>-1478</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11344</v>
+        <v>7140</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13290</v>
+        <v>7251</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1946</v>
+        <v>-111</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14363</v>
+        <v>7140</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16260</v>
+        <v>7251</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1897</v>
+        <v>-111</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10989</v>
+        <v>7140</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2301</v>
+        <v>-6122</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10989</v>
+        <v>8966</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2301</v>
+        <v>-4296</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10989</v>
+        <v>7251</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2301</v>
+        <v>-6011</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10989</v>
+        <v>11234</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2301</v>
+        <v>-2028</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10989</v>
+        <v>14280</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13290</v>
+        <v>16218</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2301</v>
+        <v>-1938</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8975</v>
+        <v>14280</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13290</v>
+        <v>16148</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4315</v>
+        <v>-1868</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1458,10 +1458,10 @@
         <v>10989</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2301</v>
+        <v>-2273</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>15</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1496,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9054</v>
+        <v>10989</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-4236</v>
+        <v>-2273</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>10989</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13290</v>
+        <v>13262</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2301</v>
+        <v>-2273</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>15</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,43 +1576,133 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>8966</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>13262</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-4296</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>10989</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>13262</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-2273</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>23-SEP-26</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-143</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D27" s="2" t="n">
         <v>7140</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>7265</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
+      <c r="E27" s="2" t="n">
+        <v>7251</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-111</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -658,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,26 +668,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14052</v>
+        <v>8946</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16434</v>
+        <v>11452</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2382</v>
+        <v>-2506</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11485</v>
+        <v>14059</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13448</v>
+        <v>16434</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1963</v>
+        <v>-2375</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>20</v>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,10 +555,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4926</v>
+        <v>4904</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>-56</v>
@@ -582,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4926</v>
+        <v>4904</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-56</v>
@@ -627,10 +645,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4926</v>
+        <v>4904</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>-56</v>
@@ -658,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8946</v>
+        <v>12414</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11452</v>
+        <v>16417</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2506</v>
+        <v>-4003</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -703,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -717,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14059</v>
+        <v>9514</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16434</v>
+        <v>11429</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2375</v>
+        <v>-1915</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>20</v>
@@ -740,6 +758,726 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>9594</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>16417</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-6823</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>12655</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>16417</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-3762</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>14064</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>16417</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-2353</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>7342</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>24-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>8328</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-1508</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>7342</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>7342</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-6215</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>9062</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-4368</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9510</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-3920</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-6102</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>19-AUG-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>14515</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>16417</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-1902</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-511</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>8983</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-4447</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>9062</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-4368</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>7342</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4904</v>
+        <v>11485</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4960</v>
+        <v>13430</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-56</v>
+        <v>-1945</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12414</v>
+        <v>9513</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16417</v>
+        <v>13430</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4003</v>
+        <v>-3917</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>20</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9514</v>
+        <v>9592</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11429</v>
+        <v>16431</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1915</v>
+        <v>-6839</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>20</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9594</v>
+        <v>13359</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16417</v>
+        <v>16431</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6823</v>
+        <v>-3072</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12655</v>
+        <v>7215</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16417</v>
+        <v>8328</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3762</v>
+        <v>-1113</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14064</v>
+        <v>7328</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16417</v>
+        <v>8836</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2353</v>
+        <v>-1508</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7328</v>
+        <v>7215</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>7342</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-14</v>
+        <v>-127</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -963,10 +963,10 @@
         <v>7215</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8328</v>
+        <v>7342</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1113</v>
+        <v>-127</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7328</v>
+        <v>7215</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8836</v>
+        <v>13430</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1508</v>
+        <v>-6215</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7215</v>
+        <v>9249</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7342</v>
+        <v>13430</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-127</v>
+        <v>-4181</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7215</v>
+        <v>9065</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7342</v>
+        <v>13430</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-127</v>
+        <v>-4365</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7215</v>
+        <v>9513</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-6215</v>
+        <v>-3917</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9062</v>
+        <v>7328</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4368</v>
+        <v>-6102</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9510</v>
+        <v>11358</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3920</v>
+        <v>-2072</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>20</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7328</v>
+        <v>10964</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-6102</v>
+        <v>-2466</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14515</v>
+        <v>8985</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16417</v>
+        <v>13430</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1902</v>
+        <v>-4445</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8983</v>
+        <v>9065</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4447</v>
+        <v>-4365</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>20</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,78 +1406,33 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9062</v>
+        <v>7215</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13430</v>
+        <v>7342</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4368</v>
+        <v>-127</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>7215</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>7342</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-127</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9513</v>
+        <v>12412</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13430</v>
+        <v>16431</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3917</v>
+        <v>-4019</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>20</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9592</v>
+        <v>9513</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16431</v>
+        <v>13430</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6839</v>
+        <v>-3917</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>20</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13359</v>
+        <v>9592</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>16431</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3072</v>
+        <v>-6839</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7215</v>
+        <v>13359</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8328</v>
+        <v>16431</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1113</v>
+        <v>-3072</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7328</v>
+        <v>7215</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8836</v>
+        <v>8328</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1508</v>
+        <v>-1113</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7215</v>
+        <v>7328</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7342</v>
+        <v>8836</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-127</v>
+        <v>-1508</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1008,10 +1008,10 @@
         <v>7215</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13430</v>
+        <v>7342</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-6215</v>
+        <v>-127</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9249</v>
+        <v>7215</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4181</v>
+        <v>-6215</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9065</v>
+        <v>9249</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4365</v>
+        <v>-4181</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>20</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9513</v>
+        <v>9065</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3917</v>
+        <v>-4365</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>20</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7328</v>
+        <v>9513</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-6102</v>
+        <v>-3917</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11358</v>
+        <v>7328</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2072</v>
+        <v>-6102</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10964</v>
+        <v>11358</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2466</v>
+        <v>-2072</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8985</v>
+        <v>10964</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4445</v>
+        <v>-2466</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9065</v>
+        <v>8985</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4365</v>
+        <v>-4445</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>20</v>
@@ -1396,43 +1396,88 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-513</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>9065</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-4365</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>23-SEP-26</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-443</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-143</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D22" s="2" t="n">
         <v>7215</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>7342</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F22" s="2" t="n">
         <v>-127</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12412</v>
+        <v>12407</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>16431</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4019</v>
+        <v>-4024</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>20</v>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9513</v>
+        <v>9508</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3917</v>
+        <v>-3922</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>20</v>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9592</v>
+        <v>9588</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>16431</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6839</v>
+        <v>-6843</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>20</v>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9249</v>
+        <v>9245</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4181</v>
+        <v>-4185</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>20</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9065</v>
+        <v>9508</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4365</v>
+        <v>-3922</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>20</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9513</v>
+        <v>7328</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3917</v>
+        <v>-6102</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7328</v>
+        <v>11353</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6102</v>
+        <v>-2077</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11358</v>
+        <v>10964</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2072</v>
+        <v>-2466</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10964</v>
+        <v>8982</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2466</v>
+        <v>-4448</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8985</v>
+        <v>9061</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>13430</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4445</v>
+        <v>-4369</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>20</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,78 +1406,33 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9065</v>
+        <v>7215</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13430</v>
+        <v>7342</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4365</v>
+        <v>-127</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>7215</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>7342</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-127</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-967</t>
+          <t>SM-443</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4904</v>
+        <v>9703</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4960</v>
+        <v>19420</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-56</v>
+        <v>-9717</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4904</v>
+        <v>12816</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4960</v>
+        <v>19420</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-56</v>
+        <v>-6604</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11485</v>
+        <v>14073</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13430</v>
+        <v>19420</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1945</v>
+        <v>-5347</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12407</v>
+        <v>14352</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16431</v>
+        <v>19420</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4024</v>
+        <v>-5068</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9508</v>
+        <v>14352</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13430</v>
+        <v>19420</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3922</v>
+        <v>-5068</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9588</v>
+        <v>16586</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16431</v>
+        <v>19420</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6843</v>
+        <v>-2834</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13359</v>
+        <v>13271</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16431</v>
+        <v>19420</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3072</v>
+        <v>-6149</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,28 +866,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7215</v>
+        <v>9397</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8328</v>
+        <v>13417</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1113</v>
+        <v>-4020</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7328</v>
+        <v>8893</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8836</v>
+        <v>9605</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1508</v>
+        <v>-712</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7215</v>
+        <v>7190</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7342</v>
+        <v>7595</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-127</v>
+        <v>-405</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7215</v>
+        <v>8893</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7342</v>
+        <v>13417</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-127</v>
+        <v>-4524</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7215</v>
+        <v>8979</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13430</v>
+        <v>13417</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6215</v>
+        <v>-4438</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9245</v>
+        <v>7664</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13430</v>
+        <v>13417</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4185</v>
+        <v>-5753</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9508</v>
+        <v>11251</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13430</v>
+        <v>13417</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3922</v>
+        <v>-2166</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>20</v>
@@ -1157,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7328</v>
+        <v>8901</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13430</v>
+        <v>13417</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-6102</v>
+        <v>-4516</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11353</v>
+        <v>8979</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13430</v>
+        <v>13417</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2077</v>
+        <v>-4438</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>20</v>
@@ -1247,192 +1247,12 @@
       <c r="I17" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-762</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>10964</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>13430</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-2466</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>8982</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>13430</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-4448</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>9061</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>13430</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-4369</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>7215</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>7342</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-127</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +542,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9703</v>
+        <v>8890</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19420</v>
+        <v>13289</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-9717</v>
+        <v>-4399</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12816</v>
+        <v>10736</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19420</v>
+        <v>13289</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6604</v>
+        <v>-2553</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>15</v>
@@ -619,7 +610,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14073</v>
+        <v>6637</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19420</v>
+        <v>6817</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-5347</v>
+        <v>-180</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14352</v>
+        <v>8818</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19420</v>
+        <v>9508</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5068</v>
+        <v>-690</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14352</v>
+        <v>7107</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19420</v>
+        <v>7217</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5068</v>
+        <v>-110</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,28 +767,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16586</v>
+        <v>7245</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>19420</v>
+        <v>7521</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-2834</v>
+        <v>-276</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13271</v>
+        <v>9071</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19420</v>
+        <v>13289</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6149</v>
+        <v>-4218</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>20</v>
@@ -844,7 +835,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9397</v>
+        <v>8890</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13417</v>
+        <v>13289</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4020</v>
+        <v>-4399</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>20</v>
@@ -887,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,28 +902,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8893</v>
+        <v>9329</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9605</v>
+        <v>13289</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-712</v>
+        <v>-3960</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7190</v>
+        <v>8266</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7595</v>
+        <v>13289</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-405</v>
+        <v>-5023</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +968,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8893</v>
+        <v>10621</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13417</v>
+        <v>13289</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4524</v>
+        <v>-2668</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8979</v>
+        <v>8813</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13417</v>
+        <v>13289</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4438</v>
+        <v>-4476</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>20</v>
@@ -1067,7 +1058,7 @@
       <c r="I13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7664</v>
+        <v>11012</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13417</v>
+        <v>13289</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5753</v>
+        <v>-2277</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-511</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11251</v>
+        <v>8890</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13417</v>
+        <v>13289</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2166</v>
+        <v>-4399</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>20</v>
@@ -1157,102 +1148,12 @@
       <c r="I15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>8901</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>13417</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-4516</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>8979</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>13417</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-4438</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
